--- a/Hydroacoustics/TAST/Seal_presence_time_TAST_ON_KH.xlsx
+++ b/Hydroacoustics/TAST/Seal_presence_time_TAST_ON_KH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khomolka\Documents\GitHub\PGST-Natural-Resources\Hydroacoustics\TAST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A2EF73D-7514-4A55-9990-89E4BF6EE6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBAAF3C-9D60-4171-9F03-9A672BBD77EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{40D757BB-DE0F-4C17-8379-E3BA6797723D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="424">
   <si>
     <t>Notes</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>May_24_2023_144714_1277</t>
-  </si>
-  <si>
-    <t>2 seal times</t>
   </si>
   <si>
     <t>Seal swims through twice</t>
@@ -1685,7 +1682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C16CD6-A87F-4533-B7C9-99441C90AE92}">
-  <dimension ref="A1:S390"/>
+  <dimension ref="A1:S389"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="28.42578125" customWidth="1"/>
@@ -1701,58 +1698,58 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" t="s">
         <v>420</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>421</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>422</v>
-      </c>
-      <c r="R1" t="s">
-        <v>423</v>
       </c>
       <c r="S1" t="s">
         <v>0</v>
@@ -1760,200 +1757,194 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="4">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="C2" s="5">
-        <v>0.15205902777777777</v>
+        <v>0.50546296296296289</v>
       </c>
       <c r="D2" s="5">
-        <v>0.15217361111111111</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.15540625</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0.15561921296296297</v>
+        <v>0.50559143518518523</v>
       </c>
       <c r="O2" s="1">
         <f>(D2-C2)+(F2-E2)+(H2-G2)+(J2-I2)+(L2-K2)</f>
-        <v>3.2754629629630494E-4</v>
+        <v>1.2847222222234222E-4</v>
       </c>
       <c r="P2" s="7">
-        <f>O2*86400</f>
-        <v>28.300000000000747</v>
+        <f t="shared" ref="P2:P64" si="0">O2*86400</f>
+        <v>11.100000000010368</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4">
         <v>45077</v>
       </c>
       <c r="C3" s="5">
-        <v>0.50546296296296289</v>
+        <v>0.54646527777777776</v>
       </c>
       <c r="D3" s="5">
-        <v>0.50559143518518523</v>
+        <v>0.54658796296296297</v>
       </c>
       <c r="O3" s="1">
-        <f>(D3-C3)+(F3-E3)+(H3-G3)+(J3-I3)+(L3-K3)</f>
-        <v>1.2847222222234222E-4</v>
+        <f t="shared" ref="O3:O65" si="1">(D3-C3)+(F3-E3)+(H3-G3)+(J3-I3)+(L3-K3)</f>
+        <v>1.2268518518521176E-4</v>
       </c>
       <c r="P3" s="7">
-        <f t="shared" ref="P3:P65" si="0">O3*86400</f>
-        <v>11.100000000010368</v>
+        <f t="shared" si="0"/>
+        <v>10.600000000002296</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4">
         <v>45077</v>
       </c>
       <c r="C4" s="5">
-        <v>0.54646527777777776</v>
+        <v>0.57803240740740736</v>
       </c>
       <c r="D4" s="5">
-        <v>0.54658796296296297</v>
+        <v>0.57821875</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.57863773148148145</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.57872916666666663</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" ref="O4:O66" si="1">(D4-C4)+(F4-E4)+(H4-G4)+(J4-I4)+(L4-K4)</f>
-        <v>1.2268518518521176E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.777777777778212E-4</v>
       </c>
       <c r="P4" s="7">
         <f t="shared" si="0"/>
-        <v>10.600000000002296</v>
+        <v>24.000000000003752</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="4">
         <v>45077</v>
       </c>
       <c r="C5" s="5">
-        <v>0.57803240740740736</v>
+        <v>0.58455092592592595</v>
       </c>
       <c r="D5" s="5">
-        <v>0.57821875</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.57863773148148145</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.57872916666666663</v>
+        <v>0.58461226851851855</v>
       </c>
       <c r="O5" s="1">
         <f t="shared" si="1"/>
-        <v>2.777777777778212E-4</v>
+        <v>6.1342592592605882E-5</v>
       </c>
       <c r="P5" s="7">
         <f t="shared" si="0"/>
-        <v>24.000000000003752</v>
+        <v>5.3000000000011482</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4">
         <v>45077</v>
       </c>
       <c r="C6" s="5">
-        <v>0.58455092592592595</v>
+        <v>0.60472453703703699</v>
       </c>
       <c r="D6" s="5">
-        <v>0.58461226851851855</v>
+        <v>0.60502662037037036</v>
       </c>
       <c r="O6" s="1">
         <f t="shared" si="1"/>
-        <v>6.1342592592605882E-5</v>
+        <v>3.0208333333336945E-4</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" si="0"/>
-        <v>5.3000000000011482</v>
+        <v>26.100000000003121</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="S6" t="s">
-        <v>10</v>
+      <c r="S6" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4">
-        <v>45077</v>
+        <v>45082</v>
       </c>
       <c r="C7" s="5">
-        <v>0.60472453703703699</v>
+        <v>0.98528356481481483</v>
       </c>
       <c r="D7" s="5">
-        <v>0.60502662037037036</v>
+        <v>0.9857407407407407</v>
       </c>
       <c r="O7" s="1">
         <f t="shared" si="1"/>
-        <v>3.0208333333336945E-4</v>
+        <v>4.5717592592586787E-4</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" si="0"/>
-        <v>26.100000000003121</v>
+        <v>39.499999999994984</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -1964,89 +1955,89 @@
         <v>45082</v>
       </c>
       <c r="C8" s="5">
-        <v>0.98528356481481483</v>
+        <v>0.99351967592592594</v>
       </c>
       <c r="D8" s="5">
-        <v>0.9857407407407407</v>
+        <v>0.99362268518518526</v>
       </c>
       <c r="O8" s="1">
         <f t="shared" si="1"/>
-        <v>4.5717592592586787E-4</v>
+        <v>1.0300925925932347E-4</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" si="0"/>
-        <v>39.499999999994984</v>
+        <v>8.9000000000055479</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>165</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4">
         <v>45082</v>
       </c>
       <c r="C9" s="5">
-        <v>0.99351967592592594</v>
+        <v>4.2717592592592592E-2</v>
       </c>
       <c r="D9" s="5">
-        <v>0.99362268518518526</v>
+        <v>4.3214120370370368E-2</v>
       </c>
       <c r="O9" s="1">
         <f t="shared" si="1"/>
-        <v>1.0300925925932347E-4</v>
+        <v>4.9652777777777629E-4</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" si="0"/>
-        <v>8.9000000000055479</v>
+        <v>42.899999999999871</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>15</v>
+        <v>401</v>
+      </c>
+      <c r="S9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="4">
         <v>45082</v>
       </c>
       <c r="C10" s="5">
-        <v>4.2717592592592592E-2</v>
+        <v>5.9660879629629626E-2</v>
       </c>
       <c r="D10" s="5">
-        <v>4.3214120370370368E-2</v>
+        <v>5.9959490740740744E-2</v>
       </c>
       <c r="O10" s="1">
         <f t="shared" si="1"/>
-        <v>4.9652777777777629E-4</v>
+        <v>2.9861111111111754E-4</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" si="0"/>
-        <v>42.899999999999871</v>
+        <v>25.800000000000555</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="S10" t="s">
-        <v>17</v>
+      <c r="S10" s="2" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -2057,89 +2048,99 @@
         <v>45082</v>
       </c>
       <c r="C11" s="5">
-        <v>5.9660879629629626E-2</v>
+        <v>7.91412037037037E-2</v>
       </c>
       <c r="D11" s="5">
-        <v>5.9959490740740744E-2</v>
+        <v>7.9363425925925921E-2</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" si="1"/>
-        <v>2.9861111111111754E-4</v>
+        <v>2.2222222222222088E-4</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" si="0"/>
-        <v>25.800000000000555</v>
+        <v>19.199999999999882</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4">
         <v>45082</v>
       </c>
       <c r="C12" s="5">
-        <v>7.91412037037037E-2</v>
+        <v>7.9824074074074075E-2</v>
       </c>
       <c r="D12" s="5">
-        <v>7.9363425925925921E-2</v>
+        <v>8.0111111111111119E-2</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="1"/>
-        <v>2.2222222222222088E-4</v>
+        <v>2.8703703703704397E-4</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" si="0"/>
-        <v>19.199999999999882</v>
+        <v>24.800000000000601</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="4">
-        <v>45082</v>
-      </c>
-      <c r="C13" s="5">
-        <v>7.9824074074074075E-2</v>
-      </c>
-      <c r="D13" s="5">
-        <v>8.0111111111111119E-2</v>
-      </c>
+        <v>45083</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.52195601851851847</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.52225694444444437</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.52275694444444443</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.52309837962962968</v>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
       <c r="O13" s="1">
         <f t="shared" si="1"/>
-        <v>2.8703703703704397E-4</v>
+        <v>6.4236111111115601E-4</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" si="0"/>
-        <v>24.800000000000601</v>
+        <v>55.50000000000388</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>22</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -2149,217 +2150,213 @@
       <c r="B14" s="4">
         <v>45083</v>
       </c>
-      <c r="C14" s="6">
-        <v>0.52195601851851847</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.52225694444444437</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.52275694444444443</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.52309837962962968</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="C14" s="5">
+        <v>0.5608946759259259</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.56138194444444445</v>
+      </c>
       <c r="O14" s="1">
         <f t="shared" si="1"/>
-        <v>6.4236111111115601E-4</v>
+        <v>4.8726851851854658E-4</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" si="0"/>
-        <v>55.50000000000388</v>
+        <v>42.100000000002424</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>201</v>
+        <v>401</v>
+      </c>
+      <c r="S14" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="4">
         <v>45083</v>
       </c>
       <c r="C15" s="5">
-        <v>0.5608946759259259</v>
+        <v>0.5899085648148148</v>
       </c>
       <c r="D15" s="5">
-        <v>0.56138194444444445</v>
+        <v>0.59002777777777771</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" si="1"/>
-        <v>4.8726851851854658E-4</v>
+        <v>1.1921296296291128E-4</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" si="0"/>
-        <v>42.100000000002424</v>
+        <v>10.299999999995535</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="4">
         <v>45083</v>
       </c>
       <c r="C16" s="5">
-        <v>0.5899085648148148</v>
+        <v>0.60074074074074069</v>
       </c>
       <c r="D16" s="5">
-        <v>0.59002777777777771</v>
+        <v>0.60151736111111109</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.602005787037037</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0.60238194444444437</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" si="1"/>
-        <v>1.1921296296291128E-4</v>
+        <v>1.1527777777777803E-3</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" si="0"/>
-        <v>10.299999999995535</v>
+        <v>99.600000000000222</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="4">
         <v>45083</v>
       </c>
       <c r="C17" s="5">
-        <v>0.60074074074074069</v>
+        <v>0.63662731481481483</v>
       </c>
       <c r="D17" s="5">
-        <v>0.60151736111111109</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0.602005787037037</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0.60238194444444437</v>
+        <v>0.63875347222222223</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" si="1"/>
-        <v>1.1527777777777803E-3</v>
+        <v>2.126157407407403E-3</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" si="0"/>
-        <v>99.600000000000222</v>
+        <v>183.69999999999962</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="S17" t="s">
-        <v>29</v>
+        <v>401</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="4">
         <v>45083</v>
       </c>
       <c r="C18" s="5">
-        <v>0.63662731481481483</v>
+        <v>0.6403888888888889</v>
       </c>
       <c r="D18" s="5">
-        <v>0.63875347222222223</v>
+        <v>0.64111342592592591</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.64217592592592598</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0.64272685185185185</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.64344097222222219</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0.64388541666666665</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.64443865740740736</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0.64471412037037035</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" si="1"/>
-        <v>2.126157407407403E-3</v>
+        <v>1.9953703703703418E-3</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" si="0"/>
-        <v>183.69999999999962</v>
+        <v>172.39999999999753</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>31</v>
+        <v>401</v>
+      </c>
+      <c r="S18" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="4">
         <v>45083</v>
       </c>
       <c r="C19" s="5">
-        <v>0.6403888888888889</v>
+        <v>0.70262499999999994</v>
       </c>
       <c r="D19" s="5">
-        <v>0.64111342592592591</v>
+        <v>0.702662037037037</v>
       </c>
       <c r="E19" s="5">
-        <v>0.64217592592592598</v>
+        <v>0.70407407407407396</v>
       </c>
       <c r="F19" s="5">
-        <v>0.64272685185185185</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.64344097222222219</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0.64388541666666665</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0.64443865740740736</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0.64471412037037035</v>
+        <v>0.70416087962962959</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" si="1"/>
-        <v>1.9953703703703418E-3</v>
+        <v>1.2384259259268227E-4</v>
       </c>
       <c r="P19" s="7">
         <f t="shared" si="0"/>
-        <v>172.39999999999753</v>
+        <v>10.700000000007748</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -2367,216 +2364,210 @@
         <v>34</v>
       </c>
       <c r="B20" s="4">
-        <v>45083</v>
+        <v>45089</v>
       </c>
       <c r="C20" s="5">
-        <v>0.70262499999999994</v>
+        <v>0.41964583333333333</v>
       </c>
       <c r="D20" s="5">
-        <v>0.702662037037037</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.70407407407407396</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.70416087962962959</v>
+        <v>0.41978587962962965</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" si="1"/>
-        <v>1.2384259259268227E-4</v>
+        <v>1.4004629629632559E-4</v>
       </c>
       <c r="P20" s="7">
         <f t="shared" si="0"/>
-        <v>10.700000000007748</v>
+        <v>12.100000000002531</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="S20" t="s">
-        <v>36</v>
+      <c r="S20" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="4">
         <v>45089</v>
       </c>
-      <c r="C21" s="5">
-        <v>0.41964583333333333</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.41978587962962965</v>
-      </c>
       <c r="O21" s="1">
         <f t="shared" si="1"/>
-        <v>1.4004629629632559E-4</v>
+        <v>0</v>
       </c>
       <c r="P21" s="7">
         <f t="shared" si="0"/>
-        <v>12.100000000002531</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="S21" s="2" t="s">
-        <v>237</v>
+      <c r="S21" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="4">
         <v>45089</v>
       </c>
+      <c r="C22" s="5">
+        <v>0.98135300925925917</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.98156597222222219</v>
+      </c>
       <c r="O22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.1296296296302586E-4</v>
       </c>
       <c r="P22" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18.400000000005434</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="S22" t="s">
-        <v>38</v>
+        <v>402</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="4">
         <v>45089</v>
       </c>
       <c r="C23" s="5">
-        <v>0.98135300925925917</v>
+        <v>0.99213425925925935</v>
       </c>
       <c r="D23" s="5">
-        <v>0.98156597222222219</v>
+        <v>0.99264351851851851</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" si="1"/>
-        <v>2.1296296296302586E-4</v>
+        <v>5.0925925925915383E-4</v>
       </c>
       <c r="P23" s="7">
         <f t="shared" si="0"/>
-        <v>18.400000000005434</v>
+        <v>43.999999999990891</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="4">
         <v>45089</v>
       </c>
       <c r="C24" s="5">
-        <v>0.99213425925925935</v>
+        <v>1.0532407407407407E-2</v>
       </c>
       <c r="D24" s="5">
-        <v>0.99264351851851851</v>
+        <v>1.0686342592592593E-2</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" si="1"/>
-        <v>5.0925925925915383E-4</v>
+        <v>1.5393518518518577E-4</v>
       </c>
       <c r="P24" s="7">
         <f t="shared" si="0"/>
-        <v>43.999999999990891</v>
+        <v>13.30000000000005</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" s="4">
         <v>45089</v>
       </c>
       <c r="C25" s="5">
-        <v>1.0532407407407407E-2</v>
+        <v>4.97650462962963E-2</v>
       </c>
       <c r="D25" s="5">
-        <v>1.0686342592592593E-2</v>
+        <v>4.9961805555555551E-2</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" si="1"/>
-        <v>1.5393518518518577E-4</v>
+        <v>1.967592592592507E-4</v>
       </c>
       <c r="P25" s="7">
         <f t="shared" si="0"/>
-        <v>13.30000000000005</v>
+        <v>16.999999999999261</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B26" s="4">
         <v>45089</v>
       </c>
       <c r="C26" s="5">
-        <v>4.97650462962963E-2</v>
+        <v>6.5887731481481485E-2</v>
       </c>
       <c r="D26" s="5">
-        <v>4.9961805555555551E-2</v>
+        <v>6.6344907407407408E-2</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="1"/>
-        <v>1.967592592592507E-4</v>
+        <v>4.5717592592592338E-4</v>
       </c>
       <c r="P26" s="7">
         <f t="shared" si="0"/>
-        <v>16.999999999999261</v>
+        <v>39.49999999999978</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>46</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -2587,162 +2578,156 @@
         <v>45089</v>
       </c>
       <c r="C27" s="5">
-        <v>6.5887731481481485E-2</v>
+        <v>9.2585648148148139E-2</v>
       </c>
       <c r="D27" s="5">
-        <v>6.6344907407407408E-2</v>
+        <v>9.2660879629629642E-2</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="1"/>
-        <v>4.5717592592592338E-4</v>
+        <v>7.5231481481502493E-5</v>
       </c>
       <c r="P27" s="7">
         <f t="shared" si="0"/>
-        <v>39.49999999999978</v>
+        <v>6.5000000000018154</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>262</v>
+        <v>401</v>
+      </c>
+      <c r="S27" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28" s="4">
         <v>45089</v>
       </c>
       <c r="C28" s="5">
-        <v>9.2585648148148139E-2</v>
+        <v>9.8409722222222218E-2</v>
       </c>
       <c r="D28" s="5">
-        <v>9.2660879629629642E-2</v>
+        <v>9.8656250000000001E-2</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" si="1"/>
-        <v>7.5231481481502493E-5</v>
+        <v>2.4652777777778301E-4</v>
       </c>
       <c r="P28" s="7">
         <f t="shared" si="0"/>
-        <v>6.5000000000018154</v>
+        <v>21.300000000000452</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="S28" t="s">
-        <v>49</v>
+      <c r="S28" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="4">
-        <v>45089</v>
+        <v>45097</v>
       </c>
       <c r="C29" s="5">
-        <v>9.8409722222222218E-2</v>
+        <v>0.9803587962962963</v>
       </c>
       <c r="D29" s="5">
-        <v>9.8656250000000001E-2</v>
+        <v>0.98040740740740739</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="1"/>
-        <v>2.4652777777778301E-4</v>
+        <v>4.8611111111096506E-5</v>
       </c>
       <c r="P29" s="7">
         <f t="shared" si="0"/>
-        <v>21.300000000000452</v>
+        <v>4.1999999999987381</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>51</v>
+        <v>401</v>
+      </c>
+      <c r="S29" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B30" s="4">
         <v>45097</v>
       </c>
       <c r="C30" s="5">
-        <v>0.9803587962962963</v>
+        <v>3.6574074074074075E-4</v>
       </c>
       <c r="D30" s="5">
-        <v>0.98040740740740739</v>
+        <v>4.0046296296296293E-4</v>
+      </c>
+      <c r="E30" s="5">
+        <v>4.3263888888888892E-3</v>
+      </c>
+      <c r="F30" s="5">
+        <v>4.4039351851851852E-3</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" si="1"/>
-        <v>4.8611111111096506E-5</v>
+        <v>1.1226851851851822E-4</v>
       </c>
       <c r="P30" s="7">
         <f t="shared" si="0"/>
-        <v>4.1999999999987381</v>
+        <v>9.6999999999999744</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B31" s="4">
-        <v>45097</v>
-      </c>
-      <c r="C31" s="5">
-        <v>3.6574074074074075E-4</v>
-      </c>
-      <c r="D31" s="5">
-        <v>4.0046296296296293E-4</v>
-      </c>
-      <c r="E31" s="5">
-        <v>4.3263888888888892E-3</v>
-      </c>
-      <c r="F31" s="5">
-        <v>4.4039351851851852E-3</v>
+        <v>45076</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" si="1"/>
-        <v>1.1226851851851822E-4</v>
+        <v>0</v>
       </c>
       <c r="P31" s="7">
         <f t="shared" si="0"/>
-        <v>9.6999999999999744</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S31" t="s">
-        <v>55</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B32" s="4">
         <v>45076</v>
@@ -2756,13 +2741,13 @@
         <v>0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S32" t="s">
-        <v>424</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -2781,18 +2766,18 @@
         <v>0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" s="4">
         <v>45076</v>
@@ -2806,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S34" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -2831,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S35" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -2856,13 +2841,13 @@
         <v>0</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S36" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -2881,18 +2866,18 @@
         <v>0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S37" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B38" s="4">
         <v>45076</v>
@@ -2906,18 +2891,18 @@
         <v>0</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B39" s="4">
         <v>45076</v>
@@ -2931,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S39" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -2956,13 +2941,13 @@
         <v>0</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -2981,18 +2966,18 @@
         <v>0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S41" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B42" s="4">
         <v>45076</v>
@@ -3006,13 +2991,13 @@
         <v>0</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -3031,13 +3016,13 @@
         <v>0</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -3056,13 +3041,13 @@
         <v>0</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -3081,13 +3066,13 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -3097,53 +3082,53 @@
       <c r="B46" s="4">
         <v>45076</v>
       </c>
+      <c r="C46" s="5">
+        <v>9.8159722222222225E-3</v>
+      </c>
+      <c r="D46" s="5">
+        <v>1.0021990740740741E-2</v>
+      </c>
       <c r="O46" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.0601851851851857E-4</v>
       </c>
       <c r="P46" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17.800000000000004</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="S46" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B47" s="4">
         <v>45076</v>
       </c>
-      <c r="C47" s="5">
-        <v>9.8159722222222225E-3</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1.0021990740740741E-2</v>
-      </c>
       <c r="O47" s="1">
         <f t="shared" si="1"/>
-        <v>2.0601851851851857E-4</v>
+        <v>0</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="0"/>
-        <v>17.800000000000004</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S47" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -3162,18 +3147,18 @@
         <v>0</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S48" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B49" s="4">
         <v>45076</v>
@@ -3187,13 +3172,13 @@
         <v>0</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S49" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -3212,13 +3197,13 @@
         <v>0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -3237,13 +3222,13 @@
         <v>0</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -3262,13 +3247,13 @@
         <v>0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -3287,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -3312,13 +3297,13 @@
         <v>0</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -3337,13 +3322,13 @@
         <v>0</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
@@ -3362,18 +3347,18 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S56" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B57" s="4">
         <v>45076</v>
@@ -3387,13 +3372,13 @@
         <v>0</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S57" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
@@ -3412,13 +3397,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
@@ -3437,13 +3422,13 @@
         <v>0</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -3462,13 +3447,13 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -3487,13 +3472,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -3512,13 +3497,13 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
@@ -3537,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -3562,13 +3547,13 @@
         <v>0</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S64" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
@@ -3583,17 +3568,17 @@
         <v>0</v>
       </c>
       <c r="P65" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="P65:P128" si="2">O65*86400</f>
         <v>0</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
@@ -3604,21 +3589,21 @@
         <v>45076</v>
       </c>
       <c r="O66" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="O66:O129" si="3">(D66-C66)+(F66-E66)+(H66-G66)+(J66-I66)+(L66-K66)</f>
         <v>0</v>
       </c>
       <c r="P66" s="7">
-        <f t="shared" ref="P66:P129" si="2">O66*86400</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
@@ -3629,7 +3614,7 @@
         <v>45076</v>
       </c>
       <c r="O67" s="1">
-        <f t="shared" ref="O67:O130" si="3">(D67-C67)+(F67-E67)+(H67-G67)+(J67-I67)+(L67-K67)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P67" s="7">
@@ -3637,13 +3622,13 @@
         <v>0</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
@@ -3662,13 +3647,13 @@
         <v>0</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
@@ -3687,13 +3672,13 @@
         <v>0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
@@ -3712,13 +3697,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
@@ -3737,13 +3722,13 @@
         <v>0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
@@ -3762,13 +3747,13 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
@@ -3787,75 +3772,75 @@
         <v>0</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="B74" s="4">
         <v>45076</v>
       </c>
+      <c r="C74" s="5">
+        <v>0.15205902777777777</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0.15217361111111111</v>
+      </c>
+      <c r="E74" s="5">
+        <v>0.15540625</v>
+      </c>
+      <c r="F74" s="5">
+        <v>0.15561921296296297</v>
+      </c>
       <c r="O74" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.2754629629630494E-4</v>
       </c>
       <c r="P74" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>28.300000000000747</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="S74" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B75" s="4">
         <v>45076</v>
       </c>
-      <c r="C75" s="5">
-        <v>0.15205902777777777</v>
-      </c>
-      <c r="D75" s="5">
-        <v>0.15217361111111111</v>
-      </c>
-      <c r="E75" s="5">
-        <v>0.15540625</v>
-      </c>
-      <c r="F75" s="5">
-        <v>0.15561921296296297</v>
-      </c>
       <c r="O75" s="1">
         <f t="shared" si="3"/>
-        <v>3.2754629629630494E-4</v>
+        <v>0</v>
       </c>
       <c r="P75" s="7">
         <f t="shared" si="2"/>
-        <v>28.300000000000747</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S75" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
@@ -3874,13 +3859,13 @@
         <v>0</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
@@ -3888,7 +3873,7 @@
         <v>111</v>
       </c>
       <c r="B77" s="4">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="O77" s="1">
         <f t="shared" si="3"/>
@@ -3899,13 +3884,13 @@
         <v>0</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
@@ -3924,13 +3909,13 @@
         <v>0</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S78" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
@@ -3949,13 +3934,13 @@
         <v>0</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S79" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
@@ -3974,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
@@ -3999,13 +3984,13 @@
         <v>0</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
@@ -4024,13 +4009,13 @@
         <v>0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S82" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
@@ -4049,13 +4034,13 @@
         <v>0</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
@@ -4074,13 +4059,13 @@
         <v>0</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
@@ -4099,13 +4084,13 @@
         <v>0</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
@@ -4124,13 +4109,13 @@
         <v>0</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
@@ -4149,13 +4134,13 @@
         <v>0</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
@@ -4174,13 +4159,13 @@
         <v>0</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S88" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
@@ -4199,13 +4184,13 @@
         <v>0</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S89" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
@@ -4224,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S90" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
@@ -4249,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S91" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
@@ -4274,13 +4259,13 @@
         <v>0</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S92" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
@@ -4299,13 +4284,13 @@
         <v>0</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S93" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
@@ -4315,63 +4300,63 @@
       <c r="B94" s="4">
         <v>45077</v>
       </c>
+      <c r="C94" s="5">
+        <v>0.62139004629629635</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.62148032407407405</v>
+      </c>
+      <c r="E94" s="6">
+        <v>0.62209490740740747</v>
+      </c>
+      <c r="F94" s="6">
+        <v>0.62219907407407404</v>
+      </c>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
       <c r="O94" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.94444444444275E-4</v>
       </c>
       <c r="P94" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16.79999999998536</v>
       </c>
       <c r="Q94" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="S94" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B95" s="4">
         <v>45077</v>
       </c>
-      <c r="C95" s="5">
-        <v>0.62139004629629635</v>
-      </c>
-      <c r="D95" s="5">
-        <v>0.62148032407407405</v>
-      </c>
-      <c r="E95" s="6">
-        <v>0.62209490740740747</v>
-      </c>
-      <c r="F95" s="6">
-        <v>0.62219907407407404</v>
-      </c>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
-      <c r="M95" s="6"/>
-      <c r="N95" s="6"/>
       <c r="O95" s="1">
         <f t="shared" si="3"/>
-        <v>1.94444444444275E-4</v>
+        <v>0</v>
       </c>
       <c r="P95" s="7">
         <f t="shared" si="2"/>
-        <v>16.79999999998536</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R95" s="1" t="s">
         <v>403</v>
       </c>
       <c r="S95" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
@@ -4390,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="Q96" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S96" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
@@ -4415,13 +4400,13 @@
         <v>0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S97" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
@@ -4440,18 +4425,18 @@
         <v>0</v>
       </c>
       <c r="Q98" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S98" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B99" s="4">
         <v>45077</v>
@@ -4465,13 +4450,13 @@
         <v>0</v>
       </c>
       <c r="Q99" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S99" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
@@ -4490,18 +4475,18 @@
         <v>0</v>
       </c>
       <c r="Q100" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S100" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B101" s="4">
         <v>45077</v>
@@ -4515,13 +4500,13 @@
         <v>0</v>
       </c>
       <c r="Q101" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S101" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
@@ -4540,13 +4525,13 @@
         <v>0</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S102" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
@@ -4565,18 +4550,18 @@
         <v>0</v>
       </c>
       <c r="Q103" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S103" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B104" s="4">
         <v>45077</v>
@@ -4590,13 +4575,13 @@
         <v>0</v>
       </c>
       <c r="Q104" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S104" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
@@ -4615,13 +4600,13 @@
         <v>0</v>
       </c>
       <c r="Q105" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S105" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
@@ -4640,13 +4625,13 @@
         <v>0</v>
       </c>
       <c r="Q106" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S106" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
@@ -4665,13 +4650,13 @@
         <v>0</v>
       </c>
       <c r="Q107" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S107" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
@@ -4690,13 +4675,13 @@
         <v>0</v>
       </c>
       <c r="Q108" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S108" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
@@ -4715,21 +4700,21 @@
         <v>0</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S109" t="s">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B110" s="4">
-        <v>45077</v>
+        <v>45082</v>
       </c>
       <c r="O110" s="1">
         <f t="shared" si="3"/>
@@ -4740,13 +4725,13 @@
         <v>0</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S110" t="s">
-        <v>149</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
@@ -4765,13 +4750,13 @@
         <v>0</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S111" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
@@ -4790,13 +4775,13 @@
         <v>0</v>
       </c>
       <c r="Q112" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S112" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
@@ -4815,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="Q113" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S113" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
@@ -4840,13 +4825,13 @@
         <v>0</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S114" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -4865,13 +4850,13 @@
         <v>0</v>
       </c>
       <c r="Q115" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S115" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
@@ -4890,13 +4875,13 @@
         <v>0</v>
       </c>
       <c r="Q116" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S116" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
@@ -4915,13 +4900,13 @@
         <v>0</v>
       </c>
       <c r="Q117" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S117" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
@@ -4940,13 +4925,13 @@
         <v>0</v>
       </c>
       <c r="Q118" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S118" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
@@ -4965,13 +4950,13 @@
         <v>0</v>
       </c>
       <c r="Q119" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S119" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
@@ -4990,13 +4975,13 @@
         <v>0</v>
       </c>
       <c r="Q120" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R120" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S120" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.25">
@@ -5015,13 +5000,13 @@
         <v>0</v>
       </c>
       <c r="Q121" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S121" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.25">
@@ -5040,13 +5025,13 @@
         <v>0</v>
       </c>
       <c r="Q122" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S122" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.25">
@@ -5065,13 +5050,13 @@
         <v>0</v>
       </c>
       <c r="Q123" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S123" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
@@ -5090,18 +5075,18 @@
         <v>0</v>
       </c>
       <c r="Q124" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S124" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B125" s="4">
         <v>45082</v>
@@ -5115,13 +5100,13 @@
         <v>0</v>
       </c>
       <c r="Q125" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R125" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S125" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.25">
@@ -5140,13 +5125,13 @@
         <v>0</v>
       </c>
       <c r="Q126" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
@@ -5165,13 +5150,13 @@
         <v>0</v>
       </c>
       <c r="Q127" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R127" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S127" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.25">
@@ -5190,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="Q128" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R128" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S128" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.25">
@@ -5211,17 +5196,17 @@
         <v>0</v>
       </c>
       <c r="P129" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="P129:P192" si="4">O129*86400</f>
         <v>0</v>
       </c>
       <c r="Q129" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S129" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.25">
@@ -5232,21 +5217,21 @@
         <v>45082</v>
       </c>
       <c r="O130" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="O130:O193" si="5">(D130-C130)+(F130-E130)+(H130-G130)+(J130-I130)+(L130-K130)</f>
         <v>0</v>
       </c>
       <c r="P130" s="7">
-        <f t="shared" ref="P130:P193" si="4">O130*86400</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q130" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S130" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.25">
@@ -5257,7 +5242,7 @@
         <v>45082</v>
       </c>
       <c r="O131" s="1">
-        <f t="shared" ref="O131:O194" si="5">(D131-C131)+(F131-E131)+(H131-G131)+(J131-I131)+(L131-K131)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P131" s="7">
@@ -5265,13 +5250,13 @@
         <v>0</v>
       </c>
       <c r="Q131" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S131" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.25">
@@ -5290,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="Q132" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S132" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.25">
@@ -5315,13 +5300,13 @@
         <v>0</v>
       </c>
       <c r="Q133" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S133" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
@@ -5340,13 +5325,13 @@
         <v>0</v>
       </c>
       <c r="Q134" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S134" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.25">
@@ -5365,13 +5350,13 @@
         <v>0</v>
       </c>
       <c r="Q135" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R135" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S135" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.25">
@@ -5390,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="Q136" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S136" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.25">
@@ -5415,18 +5400,18 @@
         <v>0</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R137" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S137" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B138" s="4">
         <v>45082</v>
@@ -5440,13 +5425,13 @@
         <v>0</v>
       </c>
       <c r="Q138" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S138" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.25">
@@ -5465,13 +5450,13 @@
         <v>0</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S139" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.25">
@@ -5490,13 +5475,13 @@
         <v>0</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S140" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.25">
@@ -5515,13 +5500,13 @@
         <v>0</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S141" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.25">
@@ -5540,13 +5525,13 @@
         <v>0</v>
       </c>
       <c r="Q142" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R142" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S142" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.25">
@@ -5565,13 +5550,13 @@
         <v>0</v>
       </c>
       <c r="Q143" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S143" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
@@ -5590,13 +5575,13 @@
         <v>0</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R144" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S144" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
@@ -5615,13 +5600,13 @@
         <v>0</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R145" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S145" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
@@ -5640,13 +5625,13 @@
         <v>0</v>
       </c>
       <c r="Q146" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S146" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
@@ -5665,13 +5650,13 @@
         <v>0</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R147" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S147" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
@@ -5690,13 +5675,13 @@
         <v>0</v>
       </c>
       <c r="Q148" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R148" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S148" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
@@ -5715,13 +5700,13 @@
         <v>0</v>
       </c>
       <c r="Q149" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R149" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S149" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
@@ -5740,13 +5725,13 @@
         <v>0</v>
       </c>
       <c r="Q150" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S150" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
@@ -5765,13 +5750,13 @@
         <v>0</v>
       </c>
       <c r="Q151" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S151" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
@@ -5790,13 +5775,13 @@
         <v>0</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S152" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
@@ -5815,13 +5800,13 @@
         <v>0</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S153" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
@@ -5829,7 +5814,7 @@
         <v>195</v>
       </c>
       <c r="B154" s="4">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="O154" s="1">
         <f t="shared" si="5"/>
@@ -5840,18 +5825,18 @@
         <v>0</v>
       </c>
       <c r="Q154" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R154" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S154" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B155" s="4">
         <v>45083</v>
@@ -5865,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="Q155" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S155" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
@@ -5890,13 +5875,13 @@
         <v>0</v>
       </c>
       <c r="Q156" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S156" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
@@ -5915,18 +5900,18 @@
         <v>0</v>
       </c>
       <c r="Q157" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S157" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B158" s="4">
         <v>45083</v>
@@ -5940,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="Q158" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S158" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.25">
@@ -5965,13 +5950,13 @@
         <v>0</v>
       </c>
       <c r="Q159" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S159" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.25">
@@ -5990,13 +5975,13 @@
         <v>0</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S160" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.25">
@@ -6015,13 +6000,13 @@
         <v>0</v>
       </c>
       <c r="Q161" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R161" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S161" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.25">
@@ -6040,13 +6025,13 @@
         <v>0</v>
       </c>
       <c r="Q162" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R162" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S162" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.25">
@@ -6056,53 +6041,53 @@
       <c r="B163" s="4">
         <v>45083</v>
       </c>
+      <c r="C163" s="5">
+        <v>0.56060069444444449</v>
+      </c>
+      <c r="D163" s="5">
+        <v>0.56069328703703702</v>
+      </c>
       <c r="O163" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9.2592592592533052E-5</v>
       </c>
       <c r="P163" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.9999999999948557</v>
       </c>
       <c r="Q163" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R163" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="S163" t="s">
-        <v>73</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B164" s="4">
         <v>45083</v>
       </c>
-      <c r="C164" s="5">
-        <v>0.56060069444444449</v>
-      </c>
-      <c r="D164" s="5">
-        <v>0.56069328703703702</v>
-      </c>
       <c r="O164" s="1">
         <f t="shared" si="5"/>
-        <v>9.2592592592533052E-5</v>
+        <v>0</v>
       </c>
       <c r="P164" s="7">
         <f t="shared" si="4"/>
-        <v>7.9999999999948557</v>
+        <v>0</v>
       </c>
       <c r="Q164" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R164" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S164" t="s">
-        <v>208</v>
+        <v>72</v>
       </c>
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.25">
@@ -6121,13 +6106,13 @@
         <v>0</v>
       </c>
       <c r="Q165" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R165" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S165" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.25">
@@ -6146,13 +6131,13 @@
         <v>0</v>
       </c>
       <c r="Q166" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R166" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S166" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.25">
@@ -6171,13 +6156,13 @@
         <v>0</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S167" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.25">
@@ -6196,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S168" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.25">
@@ -6221,13 +6206,13 @@
         <v>0</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S169" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="170" spans="1:19" x14ac:dyDescent="0.25">
@@ -6246,13 +6231,13 @@
         <v>0</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R170" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S170" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.25">
@@ -6271,13 +6256,13 @@
         <v>0</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R171" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S171" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.25">
@@ -6296,13 +6281,13 @@
         <v>0</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S172" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.25">
@@ -6321,13 +6306,13 @@
         <v>0</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R173" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S173" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="174" spans="1:19" x14ac:dyDescent="0.25">
@@ -6346,13 +6331,13 @@
         <v>0</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R174" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S174" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175" spans="1:19" x14ac:dyDescent="0.25">
@@ -6362,53 +6347,53 @@
       <c r="B175" s="4">
         <v>45083</v>
       </c>
+      <c r="C175" s="5">
+        <v>0.63164004629629633</v>
+      </c>
+      <c r="D175" s="5">
+        <v>0.63171180555555562</v>
+      </c>
       <c r="O175" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7.175925925928528E-5</v>
       </c>
       <c r="P175" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.2000000000022482</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R175" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="S175" t="s">
-        <v>73</v>
+        <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B176" s="4">
         <v>45083</v>
       </c>
-      <c r="C176" s="5">
-        <v>0.63164004629629633</v>
-      </c>
-      <c r="D176" s="5">
-        <v>0.63171180555555562</v>
-      </c>
       <c r="O176" s="1">
         <f t="shared" si="5"/>
-        <v>7.175925925928528E-5</v>
+        <v>0</v>
       </c>
       <c r="P176" s="7">
         <f t="shared" si="4"/>
-        <v>6.2000000000022482</v>
+        <v>0</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R176" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S176" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.25">
@@ -6427,13 +6412,13 @@
         <v>0</v>
       </c>
       <c r="Q177" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R177" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S177" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.25">
@@ -6452,13 +6437,13 @@
         <v>0</v>
       </c>
       <c r="Q178" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R178" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S178" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.25">
@@ -6477,13 +6462,13 @@
         <v>0</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R179" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S179" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.25">
@@ -6502,13 +6487,13 @@
         <v>0</v>
       </c>
       <c r="Q180" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R180" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S180" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.25">
@@ -6527,13 +6512,13 @@
         <v>0</v>
       </c>
       <c r="Q181" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R181" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S181" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.25">
@@ -6552,18 +6537,18 @@
         <v>0</v>
       </c>
       <c r="Q182" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R182" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S182" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B183" s="4">
         <v>45083</v>
@@ -6577,13 +6562,13 @@
         <v>0</v>
       </c>
       <c r="Q183" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R183" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S183" t="s">
-        <v>229</v>
+        <v>72</v>
       </c>
     </row>
     <row r="184" spans="1:19" x14ac:dyDescent="0.25">
@@ -6602,13 +6587,13 @@
         <v>0</v>
       </c>
       <c r="Q184" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S184" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.25">
@@ -6627,13 +6612,13 @@
         <v>0</v>
       </c>
       <c r="Q185" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R185" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S185" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.25">
@@ -6652,13 +6637,13 @@
         <v>0</v>
       </c>
       <c r="Q186" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R186" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S186" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="187" spans="1:19" x14ac:dyDescent="0.25">
@@ -6668,58 +6653,58 @@
       <c r="B187" s="4">
         <v>45083</v>
       </c>
+      <c r="C187" s="5">
+        <v>0.69880439814814821</v>
+      </c>
+      <c r="D187" s="5">
+        <v>0.69889467592592591</v>
+      </c>
       <c r="O187" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9.0277777777703072E-5</v>
       </c>
       <c r="P187" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.7999999999935454</v>
       </c>
       <c r="Q187" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R187" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="S187" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B188" s="4">
-        <v>45083</v>
-      </c>
-      <c r="C188" s="5">
-        <v>0.69880439814814821</v>
-      </c>
-      <c r="D188" s="5">
-        <v>0.69889467592592591</v>
+        <v>45089</v>
       </c>
       <c r="O188" s="1">
         <f t="shared" si="5"/>
-        <v>9.0277777777703072E-5</v>
+        <v>0</v>
       </c>
       <c r="P188" s="7">
         <f t="shared" si="4"/>
-        <v>7.7999999999935454</v>
+        <v>0</v>
       </c>
       <c r="Q188" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R188" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S188" t="s">
-        <v>235</v>
+        <v>72</v>
       </c>
     </row>
     <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B189" s="4">
         <v>45089</v>
@@ -6733,13 +6718,13 @@
         <v>0</v>
       </c>
       <c r="Q189" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R189" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S189" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="190" spans="1:19" x14ac:dyDescent="0.25">
@@ -6758,13 +6743,13 @@
         <v>0</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R190" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S190" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.25">
@@ -6783,13 +6768,13 @@
         <v>0</v>
       </c>
       <c r="Q191" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R191" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S191" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="192" spans="1:19" x14ac:dyDescent="0.25">
@@ -6808,18 +6793,18 @@
         <v>0</v>
       </c>
       <c r="Q192" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R192" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S192" t="s">
-        <v>73</v>
+        <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B193" s="4">
         <v>45089</v>
@@ -6829,17 +6814,17 @@
         <v>0</v>
       </c>
       <c r="P193" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="P193:P256" si="6">O193*86400</f>
         <v>0</v>
       </c>
       <c r="Q193" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R193" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S193" t="s">
-        <v>242</v>
+        <v>72</v>
       </c>
     </row>
     <row r="194" spans="1:19" x14ac:dyDescent="0.25">
@@ -6850,21 +6835,21 @@
         <v>45089</v>
       </c>
       <c r="O194" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="O194:O257" si="7">(D194-C194)+(F194-E194)+(H194-G194)+(J194-I194)+(L194-K194)</f>
         <v>0</v>
       </c>
       <c r="P194" s="7">
-        <f t="shared" ref="P194:P257" si="6">O194*86400</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q194" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R194" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S194" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="195" spans="1:19" x14ac:dyDescent="0.25">
@@ -6875,7 +6860,7 @@
         <v>45089</v>
       </c>
       <c r="O195" s="1">
-        <f t="shared" ref="O195:O258" si="7">(D195-C195)+(F195-E195)+(H195-G195)+(J195-I195)+(L195-K195)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P195" s="7">
@@ -6883,13 +6868,13 @@
         <v>0</v>
       </c>
       <c r="Q195" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R195" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S195" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="196" spans="1:19" x14ac:dyDescent="0.25">
@@ -6908,13 +6893,13 @@
         <v>0</v>
       </c>
       <c r="Q196" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R196" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S196" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.25">
@@ -6933,13 +6918,13 @@
         <v>0</v>
       </c>
       <c r="Q197" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R197" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S197" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.25">
@@ -6958,13 +6943,13 @@
         <v>0</v>
       </c>
       <c r="Q198" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R198" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S198" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.25">
@@ -6983,13 +6968,13 @@
         <v>0</v>
       </c>
       <c r="Q199" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R199" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S199" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.25">
@@ -7008,13 +6993,13 @@
         <v>0</v>
       </c>
       <c r="Q200" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R200" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S200" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="201" spans="1:19" x14ac:dyDescent="0.25">
@@ -7033,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="Q201" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R201" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S201" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="202" spans="1:19" x14ac:dyDescent="0.25">
@@ -7058,13 +7043,13 @@
         <v>0</v>
       </c>
       <c r="Q202" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R202" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S202" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.25">
@@ -7083,13 +7068,13 @@
         <v>0</v>
       </c>
       <c r="Q203" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R203" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S203" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="204" spans="1:19" x14ac:dyDescent="0.25">
@@ -7108,13 +7093,13 @@
         <v>0</v>
       </c>
       <c r="Q204" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R204" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S204" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="205" spans="1:19" x14ac:dyDescent="0.25">
@@ -7133,13 +7118,13 @@
         <v>0</v>
       </c>
       <c r="Q205" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R205" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S205" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.25">
@@ -7158,13 +7143,13 @@
         <v>0</v>
       </c>
       <c r="Q206" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R206" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S206" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="207" spans="1:19" x14ac:dyDescent="0.25">
@@ -7183,13 +7168,13 @@
         <v>0</v>
       </c>
       <c r="Q207" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R207" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S207" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="208" spans="1:19" x14ac:dyDescent="0.25">
@@ -7208,13 +7193,13 @@
         <v>0</v>
       </c>
       <c r="Q208" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R208" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S208" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="209" spans="1:19" x14ac:dyDescent="0.25">
@@ -7233,13 +7218,13 @@
         <v>0</v>
       </c>
       <c r="Q209" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R209" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S209" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="210" spans="1:19" x14ac:dyDescent="0.25">
@@ -7258,13 +7243,13 @@
         <v>0</v>
       </c>
       <c r="Q210" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R210" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S210" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="211" spans="1:19" x14ac:dyDescent="0.25">
@@ -7283,18 +7268,18 @@
         <v>0</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S211" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B212" s="4">
         <v>45089</v>
@@ -7308,13 +7293,13 @@
         <v>0</v>
       </c>
       <c r="Q212" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R212" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S212" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="213" spans="1:19" x14ac:dyDescent="0.25">
@@ -7333,13 +7318,13 @@
         <v>0</v>
       </c>
       <c r="Q213" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R213" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S213" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="214" spans="1:19" x14ac:dyDescent="0.25">
@@ -7358,13 +7343,13 @@
         <v>0</v>
       </c>
       <c r="Q214" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R214" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S214" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="215" spans="1:19" x14ac:dyDescent="0.25">
@@ -7383,13 +7368,13 @@
         <v>0</v>
       </c>
       <c r="Q215" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R215" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S215" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="216" spans="1:19" x14ac:dyDescent="0.25">
@@ -7408,13 +7393,13 @@
         <v>0</v>
       </c>
       <c r="Q216" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R216" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S216" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="217" spans="1:19" x14ac:dyDescent="0.25">
@@ -7433,13 +7418,13 @@
         <v>0</v>
       </c>
       <c r="Q217" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R217" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S217" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="218" spans="1:19" x14ac:dyDescent="0.25">
@@ -7458,13 +7443,13 @@
         <v>0</v>
       </c>
       <c r="Q218" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R218" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S218" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.25">
@@ -7483,13 +7468,13 @@
         <v>0</v>
       </c>
       <c r="Q219" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R219" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S219" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.25">
@@ -7508,13 +7493,13 @@
         <v>0</v>
       </c>
       <c r="Q220" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R220" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S220" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.25">
@@ -7533,13 +7518,13 @@
         <v>0</v>
       </c>
       <c r="Q221" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R221" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S221" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.25">
@@ -7558,13 +7543,13 @@
         <v>0</v>
       </c>
       <c r="Q222" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R222" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.25">
@@ -7574,53 +7559,53 @@
       <c r="B223" s="4">
         <v>45089</v>
       </c>
+      <c r="C223" s="5">
+        <v>0.14319675925925926</v>
+      </c>
+      <c r="D223" s="5">
+        <v>0.14322916666666666</v>
+      </c>
       <c r="O223" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.240740740739767E-5</v>
       </c>
       <c r="P223" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2.7999999999991587</v>
       </c>
       <c r="Q223" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R223" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="S223" t="s">
-        <v>73</v>
+        <v>274</v>
       </c>
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B224" s="4">
         <v>45089</v>
       </c>
-      <c r="C224" s="5">
-        <v>0.14319675925925926</v>
-      </c>
-      <c r="D224" s="5">
-        <v>0.14322916666666666</v>
-      </c>
       <c r="O224" s="1">
         <f t="shared" si="7"/>
-        <v>3.240740740739767E-5</v>
+        <v>0</v>
       </c>
       <c r="P224" s="7">
         <f t="shared" si="6"/>
-        <v>2.7999999999991587</v>
+        <v>0</v>
       </c>
       <c r="Q224" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R224" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S224" t="s">
-        <v>275</v>
+        <v>72</v>
       </c>
     </row>
     <row r="225" spans="1:19" x14ac:dyDescent="0.25">
@@ -7639,13 +7624,13 @@
         <v>0</v>
       </c>
       <c r="Q225" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R225" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S225" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="226" spans="1:19" x14ac:dyDescent="0.25">
@@ -7664,13 +7649,13 @@
         <v>0</v>
       </c>
       <c r="Q226" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R226" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S226" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="227" spans="1:19" x14ac:dyDescent="0.25">
@@ -7689,13 +7674,13 @@
         <v>0</v>
       </c>
       <c r="Q227" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R227" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S227" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="228" spans="1:19" x14ac:dyDescent="0.25">
@@ -7703,7 +7688,7 @@
         <v>279</v>
       </c>
       <c r="B228" s="4">
-        <v>45089</v>
+        <v>45090</v>
       </c>
       <c r="O228" s="1">
         <f t="shared" si="7"/>
@@ -7714,13 +7699,13 @@
         <v>0</v>
       </c>
       <c r="Q228" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R228" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S228" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="229" spans="1:19" x14ac:dyDescent="0.25">
@@ -7739,13 +7724,13 @@
         <v>0</v>
       </c>
       <c r="Q229" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R229" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S229" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="230" spans="1:19" x14ac:dyDescent="0.25">
@@ -7764,13 +7749,13 @@
         <v>0</v>
       </c>
       <c r="Q230" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R230" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S230" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="231" spans="1:19" x14ac:dyDescent="0.25">
@@ -7789,13 +7774,13 @@
         <v>0</v>
       </c>
       <c r="Q231" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R231" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S231" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="232" spans="1:19" x14ac:dyDescent="0.25">
@@ -7814,13 +7799,13 @@
         <v>0</v>
       </c>
       <c r="Q232" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R232" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S232" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="233" spans="1:19" x14ac:dyDescent="0.25">
@@ -7839,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="Q233" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R233" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S233" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="234" spans="1:19" x14ac:dyDescent="0.25">
@@ -7864,13 +7849,13 @@
         <v>0</v>
       </c>
       <c r="Q234" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R234" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S234" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="235" spans="1:19" x14ac:dyDescent="0.25">
@@ -7889,13 +7874,13 @@
         <v>0</v>
       </c>
       <c r="Q235" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S235" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.25">
@@ -7914,13 +7899,13 @@
         <v>0</v>
       </c>
       <c r="Q236" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R236" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S236" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.25">
@@ -7939,13 +7924,13 @@
         <v>0</v>
       </c>
       <c r="Q237" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R237" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S237" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.25">
@@ -7964,13 +7949,13 @@
         <v>0</v>
       </c>
       <c r="Q238" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R238" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S238" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.25">
@@ -7989,13 +7974,13 @@
         <v>0</v>
       </c>
       <c r="Q239" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R239" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S239" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.25">
@@ -8014,13 +7999,13 @@
         <v>0</v>
       </c>
       <c r="Q240" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R240" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S240" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="241" spans="1:19" x14ac:dyDescent="0.25">
@@ -8039,13 +8024,13 @@
         <v>0</v>
       </c>
       <c r="Q241" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R241" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S241" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="242" spans="1:19" x14ac:dyDescent="0.25">
@@ -8064,13 +8049,13 @@
         <v>0</v>
       </c>
       <c r="Q242" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R242" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S242" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="243" spans="1:19" x14ac:dyDescent="0.25">
@@ -8089,13 +8074,13 @@
         <v>0</v>
       </c>
       <c r="Q243" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R243" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S243" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="244" spans="1:19" x14ac:dyDescent="0.25">
@@ -8114,18 +8099,18 @@
         <v>0</v>
       </c>
       <c r="Q244" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R244" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S244" t="s">
-        <v>73</v>
+        <v>296</v>
       </c>
     </row>
     <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B245" s="4">
         <v>45090</v>
@@ -8139,13 +8124,13 @@
         <v>0</v>
       </c>
       <c r="Q245" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R245" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S245" t="s">
-        <v>297</v>
+        <v>72</v>
       </c>
     </row>
     <row r="246" spans="1:19" x14ac:dyDescent="0.25">
@@ -8164,13 +8149,13 @@
         <v>0</v>
       </c>
       <c r="Q246" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R246" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S246" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="247" spans="1:19" x14ac:dyDescent="0.25">
@@ -8189,13 +8174,13 @@
         <v>0</v>
       </c>
       <c r="Q247" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R247" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S247" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="248" spans="1:19" x14ac:dyDescent="0.25">
@@ -8214,13 +8199,13 @@
         <v>0</v>
       </c>
       <c r="Q248" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R248" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S248" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="249" spans="1:19" x14ac:dyDescent="0.25">
@@ -8230,53 +8215,53 @@
       <c r="B249" s="4">
         <v>45090</v>
       </c>
+      <c r="C249" s="5">
+        <v>0.60212037037037036</v>
+      </c>
+      <c r="D249" s="5">
+        <v>0.60454745370370377</v>
+      </c>
       <c r="O249" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.427083333333413E-3</v>
       </c>
       <c r="P249" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>209.70000000000687</v>
       </c>
       <c r="Q249" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R249" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="S249" t="s">
-        <v>73</v>
+        <v>402</v>
+      </c>
+      <c r="S249" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B250" s="4">
         <v>45090</v>
       </c>
-      <c r="C250" s="5">
-        <v>0.60212037037037036</v>
-      </c>
-      <c r="D250" s="5">
-        <v>0.60454745370370377</v>
-      </c>
       <c r="O250" s="1">
         <f t="shared" si="7"/>
-        <v>2.427083333333413E-3</v>
+        <v>0</v>
       </c>
       <c r="P250" s="7">
         <f t="shared" si="6"/>
-        <v>209.70000000000687</v>
+        <v>0</v>
       </c>
       <c r="Q250" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="S250" s="2" t="s">
-        <v>303</v>
+      <c r="S250" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="251" spans="1:19" x14ac:dyDescent="0.25">
@@ -8295,13 +8280,13 @@
         <v>0</v>
       </c>
       <c r="Q251" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R251" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S251" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="252" spans="1:19" x14ac:dyDescent="0.25">
@@ -8320,13 +8305,13 @@
         <v>0</v>
       </c>
       <c r="Q252" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R252" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S252" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="253" spans="1:19" x14ac:dyDescent="0.25">
@@ -8345,13 +8330,13 @@
         <v>0</v>
       </c>
       <c r="Q253" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R253" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S253" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="254" spans="1:19" x14ac:dyDescent="0.25">
@@ -8370,13 +8355,13 @@
         <v>0</v>
       </c>
       <c r="Q254" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R254" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S254" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="255" spans="1:19" x14ac:dyDescent="0.25">
@@ -8395,13 +8380,13 @@
         <v>0</v>
       </c>
       <c r="Q255" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R255" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S255" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="256" spans="1:19" x14ac:dyDescent="0.25">
@@ -8420,13 +8405,13 @@
         <v>0</v>
       </c>
       <c r="Q256" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R256" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S256" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="257" spans="1:19" x14ac:dyDescent="0.25">
@@ -8441,17 +8426,17 @@
         <v>0</v>
       </c>
       <c r="P257" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="P257:P320" si="8">O257*86400</f>
         <v>0</v>
       </c>
       <c r="Q257" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R257" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S257" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="258" spans="1:19" x14ac:dyDescent="0.25">
@@ -8462,21 +8447,21 @@
         <v>45090</v>
       </c>
       <c r="O258" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="O258:O321" si="9">(D258-C258)+(F258-E258)+(H258-G258)+(J258-I258)+(L258-K258)</f>
         <v>0</v>
       </c>
       <c r="P258" s="7">
-        <f t="shared" ref="P258:P321" si="8">O258*86400</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q258" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R258" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S258" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="259" spans="1:19" x14ac:dyDescent="0.25">
@@ -8487,7 +8472,7 @@
         <v>45090</v>
       </c>
       <c r="O259" s="1">
-        <f t="shared" ref="O259:O322" si="9">(D259-C259)+(F259-E259)+(H259-G259)+(J259-I259)+(L259-K259)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P259" s="7">
@@ -8495,13 +8480,13 @@
         <v>0</v>
       </c>
       <c r="Q259" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R259" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S259" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="260" spans="1:19" x14ac:dyDescent="0.25">
@@ -8520,13 +8505,13 @@
         <v>0</v>
       </c>
       <c r="Q260" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S260" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="261" spans="1:19" x14ac:dyDescent="0.25">
@@ -8545,13 +8530,13 @@
         <v>0</v>
       </c>
       <c r="Q261" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S261" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="262" spans="1:19" x14ac:dyDescent="0.25">
@@ -8570,13 +8555,13 @@
         <v>0</v>
       </c>
       <c r="Q262" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S262" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="263" spans="1:19" x14ac:dyDescent="0.25">
@@ -8595,13 +8580,13 @@
         <v>0</v>
       </c>
       <c r="Q263" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S263" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="264" spans="1:19" x14ac:dyDescent="0.25">
@@ -8620,13 +8605,13 @@
         <v>0</v>
       </c>
       <c r="Q264" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R264" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S264" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="265" spans="1:19" x14ac:dyDescent="0.25">
@@ -8645,13 +8630,13 @@
         <v>0</v>
       </c>
       <c r="Q265" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S265" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="266" spans="1:19" x14ac:dyDescent="0.25">
@@ -8670,13 +8655,13 @@
         <v>0</v>
       </c>
       <c r="Q266" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S266" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="267" spans="1:19" x14ac:dyDescent="0.25">
@@ -8695,13 +8680,13 @@
         <v>0</v>
       </c>
       <c r="Q267" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S267" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="268" spans="1:19" x14ac:dyDescent="0.25">
@@ -8720,13 +8705,13 @@
         <v>0</v>
       </c>
       <c r="Q268" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S268" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="269" spans="1:19" x14ac:dyDescent="0.25">
@@ -8734,7 +8719,7 @@
         <v>322</v>
       </c>
       <c r="B269" s="4">
-        <v>45090</v>
+        <v>45097</v>
       </c>
       <c r="O269" s="1">
         <f t="shared" si="9"/>
@@ -8745,18 +8730,18 @@
         <v>0</v>
       </c>
       <c r="Q269" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R269" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S269" t="s">
-        <v>73</v>
+        <v>323</v>
       </c>
     </row>
     <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B270" s="4">
         <v>45097</v>
@@ -8770,13 +8755,13 @@
         <v>0</v>
       </c>
       <c r="Q270" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R270" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S270" t="s">
-        <v>324</v>
+        <v>72</v>
       </c>
     </row>
     <row r="271" spans="1:19" x14ac:dyDescent="0.25">
@@ -8795,13 +8780,13 @@
         <v>0</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R271" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S271" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="272" spans="1:19" x14ac:dyDescent="0.25">
@@ -8820,13 +8805,13 @@
         <v>0</v>
       </c>
       <c r="Q272" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R272" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S272" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="273" spans="1:19" x14ac:dyDescent="0.25">
@@ -8845,13 +8830,13 @@
         <v>0</v>
       </c>
       <c r="Q273" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R273" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S273" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="274" spans="1:19" x14ac:dyDescent="0.25">
@@ -8870,13 +8855,13 @@
         <v>0</v>
       </c>
       <c r="Q274" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R274" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S274" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="275" spans="1:19" x14ac:dyDescent="0.25">
@@ -8895,13 +8880,13 @@
         <v>0</v>
       </c>
       <c r="Q275" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R275" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S275" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="276" spans="1:19" x14ac:dyDescent="0.25">
@@ -8920,13 +8905,13 @@
         <v>0</v>
       </c>
       <c r="Q276" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S276" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="277" spans="1:19" x14ac:dyDescent="0.25">
@@ -8945,13 +8930,13 @@
         <v>0</v>
       </c>
       <c r="Q277" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R277" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S277" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="278" spans="1:19" x14ac:dyDescent="0.25">
@@ -8970,13 +8955,13 @@
         <v>0</v>
       </c>
       <c r="Q278" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R278" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S278" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="279" spans="1:19" x14ac:dyDescent="0.25">
@@ -8995,13 +8980,13 @@
         <v>0</v>
       </c>
       <c r="Q279" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R279" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S279" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="280" spans="1:19" x14ac:dyDescent="0.25">
@@ -9020,13 +9005,13 @@
         <v>0</v>
       </c>
       <c r="Q280" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R280" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S280" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="281" spans="1:19" x14ac:dyDescent="0.25">
@@ -9045,13 +9030,13 @@
         <v>0</v>
       </c>
       <c r="Q281" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R281" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S281" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="282" spans="1:19" x14ac:dyDescent="0.25">
@@ -9070,13 +9055,13 @@
         <v>0</v>
       </c>
       <c r="Q282" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R282" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S282" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="283" spans="1:19" x14ac:dyDescent="0.25">
@@ -9095,13 +9080,13 @@
         <v>0</v>
       </c>
       <c r="Q283" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R283" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S283" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="284" spans="1:19" x14ac:dyDescent="0.25">
@@ -9120,13 +9105,13 @@
         <v>0</v>
       </c>
       <c r="Q284" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S284" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="285" spans="1:19" x14ac:dyDescent="0.25">
@@ -9145,13 +9130,13 @@
         <v>0</v>
       </c>
       <c r="Q285" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R285" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S285" t="s">
-        <v>73</v>
+        <v>341</v>
       </c>
     </row>
     <row r="286" spans="1:19" x14ac:dyDescent="0.25">
@@ -9170,10 +9155,10 @@
         <v>0</v>
       </c>
       <c r="Q286" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R286" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S286" t="s">
         <v>342</v>
@@ -9181,7 +9166,7 @@
     </row>
     <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B287" s="4">
         <v>45097</v>
@@ -9195,13 +9180,13 @@
         <v>0</v>
       </c>
       <c r="Q287" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R287" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S287" t="s">
-        <v>343</v>
+        <v>72</v>
       </c>
     </row>
     <row r="288" spans="1:19" x14ac:dyDescent="0.25">
@@ -9220,13 +9205,13 @@
         <v>0</v>
       </c>
       <c r="Q288" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R288" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S288" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="289" spans="1:19" x14ac:dyDescent="0.25">
@@ -9245,13 +9230,13 @@
         <v>0</v>
       </c>
       <c r="Q289" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R289" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S289" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="290" spans="1:19" x14ac:dyDescent="0.25">
@@ -9270,13 +9255,13 @@
         <v>0</v>
       </c>
       <c r="Q290" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R290" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S290" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="291" spans="1:19" x14ac:dyDescent="0.25">
@@ -9295,13 +9280,13 @@
         <v>0</v>
       </c>
       <c r="Q291" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R291" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S291" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="292" spans="1:19" x14ac:dyDescent="0.25">
@@ -9320,13 +9305,13 @@
         <v>0</v>
       </c>
       <c r="Q292" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R292" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S292" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="293" spans="1:19" x14ac:dyDescent="0.25">
@@ -9345,13 +9330,13 @@
         <v>0</v>
       </c>
       <c r="Q293" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R293" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S293" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="294" spans="1:19" x14ac:dyDescent="0.25">
@@ -9370,13 +9355,13 @@
         <v>0</v>
       </c>
       <c r="Q294" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R294" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S294" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="295" spans="1:19" x14ac:dyDescent="0.25">
@@ -9395,13 +9380,13 @@
         <v>0</v>
       </c>
       <c r="Q295" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R295" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S295" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="296" spans="1:19" x14ac:dyDescent="0.25">
@@ -9420,13 +9405,13 @@
         <v>0</v>
       </c>
       <c r="Q296" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R296" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S296" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="297" spans="1:19" x14ac:dyDescent="0.25">
@@ -9445,13 +9430,13 @@
         <v>0</v>
       </c>
       <c r="Q297" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R297" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S297" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="298" spans="1:19" x14ac:dyDescent="0.25">
@@ -9470,13 +9455,13 @@
         <v>0</v>
       </c>
       <c r="Q298" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R298" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S298" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="299" spans="1:19" x14ac:dyDescent="0.25">
@@ -9495,13 +9480,13 @@
         <v>0</v>
       </c>
       <c r="Q299" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R299" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S299" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="300" spans="1:19" x14ac:dyDescent="0.25">
@@ -9520,13 +9505,13 @@
         <v>0</v>
       </c>
       <c r="Q300" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R300" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S300" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="301" spans="1:19" x14ac:dyDescent="0.25">
@@ -9545,13 +9530,13 @@
         <v>0</v>
       </c>
       <c r="Q301" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R301" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S301" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="302" spans="1:19" x14ac:dyDescent="0.25">
@@ -9570,13 +9555,13 @@
         <v>0</v>
       </c>
       <c r="Q302" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R302" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S302" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="303" spans="1:19" x14ac:dyDescent="0.25">
@@ -9595,13 +9580,13 @@
         <v>0</v>
       </c>
       <c r="Q303" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R303" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S303" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="304" spans="1:19" x14ac:dyDescent="0.25">
@@ -9620,13 +9605,13 @@
         <v>0</v>
       </c>
       <c r="Q304" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R304" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S304" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="305" spans="1:19" x14ac:dyDescent="0.25">
@@ -9645,13 +9630,13 @@
         <v>0</v>
       </c>
       <c r="Q305" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R305" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S305" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="306" spans="1:19" x14ac:dyDescent="0.25">
@@ -9670,13 +9655,13 @@
         <v>0</v>
       </c>
       <c r="Q306" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R306" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S306" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="307" spans="1:19" x14ac:dyDescent="0.25">
@@ -9684,7 +9669,7 @@
         <v>363</v>
       </c>
       <c r="B307" s="4">
-        <v>45097</v>
+        <v>45098</v>
       </c>
       <c r="O307" s="1">
         <f t="shared" si="9"/>
@@ -9695,13 +9680,13 @@
         <v>0</v>
       </c>
       <c r="Q307" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R307" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S307" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="308" spans="1:19" x14ac:dyDescent="0.25">
@@ -9720,13 +9705,13 @@
         <v>0</v>
       </c>
       <c r="Q308" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R308" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S308" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="309" spans="1:19" x14ac:dyDescent="0.25">
@@ -9745,13 +9730,13 @@
         <v>0</v>
       </c>
       <c r="Q309" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R309" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S309" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="310" spans="1:19" x14ac:dyDescent="0.25">
@@ -9770,13 +9755,13 @@
         <v>0</v>
       </c>
       <c r="Q310" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R310" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S310" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="311" spans="1:19" x14ac:dyDescent="0.25">
@@ -9795,13 +9780,13 @@
         <v>0</v>
       </c>
       <c r="Q311" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R311" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S311" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="312" spans="1:19" x14ac:dyDescent="0.25">
@@ -9820,13 +9805,13 @@
         <v>0</v>
       </c>
       <c r="Q312" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R312" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S312" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="313" spans="1:19" x14ac:dyDescent="0.25">
@@ -9845,13 +9830,13 @@
         <v>0</v>
       </c>
       <c r="Q313" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R313" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S313" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="314" spans="1:19" x14ac:dyDescent="0.25">
@@ -9870,13 +9855,13 @@
         <v>0</v>
       </c>
       <c r="Q314" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R314" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S314" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="315" spans="1:19" x14ac:dyDescent="0.25">
@@ -9895,13 +9880,13 @@
         <v>0</v>
       </c>
       <c r="Q315" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R315" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S315" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="316" spans="1:19" x14ac:dyDescent="0.25">
@@ -9920,13 +9905,13 @@
         <v>0</v>
       </c>
       <c r="Q316" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R316" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S316" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="317" spans="1:19" x14ac:dyDescent="0.25">
@@ -9945,13 +9930,13 @@
         <v>0</v>
       </c>
       <c r="Q317" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R317" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S317" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="318" spans="1:19" x14ac:dyDescent="0.25">
@@ -9970,13 +9955,13 @@
         <v>0</v>
       </c>
       <c r="Q318" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R318" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S318" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="319" spans="1:19" x14ac:dyDescent="0.25">
@@ -9995,13 +9980,13 @@
         <v>0</v>
       </c>
       <c r="Q319" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R319" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S319" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="320" spans="1:19" x14ac:dyDescent="0.25">
@@ -10020,13 +10005,13 @@
         <v>0</v>
       </c>
       <c r="Q320" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R320" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S320" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="321" spans="1:19" x14ac:dyDescent="0.25">
@@ -10041,17 +10026,17 @@
         <v>0</v>
       </c>
       <c r="P321" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="P321:P344" si="10">O321*86400</f>
         <v>0</v>
       </c>
       <c r="Q321" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R321" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S321" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="322" spans="1:19" x14ac:dyDescent="0.25">
@@ -10062,21 +10047,21 @@
         <v>45098</v>
       </c>
       <c r="O322" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="O322:O344" si="11">(D322-C322)+(F322-E322)+(H322-G322)+(J322-I322)+(L322-K322)</f>
         <v>0</v>
       </c>
       <c r="P322" s="7">
-        <f t="shared" ref="P322:P345" si="10">O322*86400</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Q322" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R322" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S322" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="323" spans="1:19" x14ac:dyDescent="0.25">
@@ -10087,7 +10072,7 @@
         <v>45098</v>
       </c>
       <c r="O323" s="1">
-        <f t="shared" ref="O323:O345" si="11">(D323-C323)+(F323-E323)+(H323-G323)+(J323-I323)+(L323-K323)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P323" s="7">
@@ -10095,13 +10080,13 @@
         <v>0</v>
       </c>
       <c r="Q323" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R323" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S323" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="324" spans="1:19" x14ac:dyDescent="0.25">
@@ -10120,13 +10105,13 @@
         <v>0</v>
       </c>
       <c r="Q324" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R324" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S324" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="325" spans="1:19" x14ac:dyDescent="0.25">
@@ -10145,13 +10130,13 @@
         <v>0</v>
       </c>
       <c r="Q325" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R325" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S325" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="326" spans="1:19" x14ac:dyDescent="0.25">
@@ -10170,13 +10155,13 @@
         <v>0</v>
       </c>
       <c r="Q326" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R326" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S326" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="327" spans="1:19" x14ac:dyDescent="0.25">
@@ -10195,13 +10180,13 @@
         <v>0</v>
       </c>
       <c r="Q327" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R327" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S327" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="328" spans="1:19" x14ac:dyDescent="0.25">
@@ -10220,13 +10205,13 @@
         <v>0</v>
       </c>
       <c r="Q328" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R328" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S328" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="329" spans="1:19" x14ac:dyDescent="0.25">
@@ -10245,13 +10230,13 @@
         <v>0</v>
       </c>
       <c r="Q329" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R329" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S329" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="330" spans="1:19" x14ac:dyDescent="0.25">
@@ -10270,13 +10255,13 @@
         <v>0</v>
       </c>
       <c r="Q330" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R330" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S330" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="331" spans="1:19" x14ac:dyDescent="0.25">
@@ -10295,13 +10280,13 @@
         <v>0</v>
       </c>
       <c r="Q331" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R331" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S331" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="332" spans="1:19" x14ac:dyDescent="0.25">
@@ -10320,13 +10305,13 @@
         <v>0</v>
       </c>
       <c r="Q332" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R332" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S332" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="333" spans="1:19" x14ac:dyDescent="0.25">
@@ -10345,13 +10330,13 @@
         <v>0</v>
       </c>
       <c r="Q333" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R333" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S333" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="334" spans="1:19" x14ac:dyDescent="0.25">
@@ -10370,13 +10355,13 @@
         <v>0</v>
       </c>
       <c r="Q334" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R334" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S334" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="335" spans="1:19" x14ac:dyDescent="0.25">
@@ -10395,13 +10380,13 @@
         <v>0</v>
       </c>
       <c r="Q335" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R335" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S335" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="336" spans="1:19" x14ac:dyDescent="0.25">
@@ -10420,13 +10405,13 @@
         <v>0</v>
       </c>
       <c r="Q336" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R336" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S336" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="337" spans="1:19" x14ac:dyDescent="0.25">
@@ -10445,13 +10430,13 @@
         <v>0</v>
       </c>
       <c r="Q337" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R337" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S337" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="338" spans="1:19" x14ac:dyDescent="0.25">
@@ -10470,13 +10455,13 @@
         <v>0</v>
       </c>
       <c r="Q338" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R338" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S338" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="339" spans="1:19" x14ac:dyDescent="0.25">
@@ -10495,13 +10480,13 @@
         <v>0</v>
       </c>
       <c r="Q339" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R339" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S339" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="340" spans="1:19" x14ac:dyDescent="0.25">
@@ -10520,13 +10505,13 @@
         <v>0</v>
       </c>
       <c r="Q340" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R340" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S340" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="341" spans="1:19" x14ac:dyDescent="0.25">
@@ -10545,13 +10530,13 @@
         <v>0</v>
       </c>
       <c r="Q341" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R341" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S341" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="342" spans="1:19" x14ac:dyDescent="0.25">
@@ -10570,13 +10555,13 @@
         <v>0</v>
       </c>
       <c r="Q342" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R342" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S342" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="343" spans="1:19" x14ac:dyDescent="0.25">
@@ -10595,13 +10580,13 @@
         <v>0</v>
       </c>
       <c r="Q343" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R343" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S343" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="344" spans="1:19" x14ac:dyDescent="0.25">
@@ -10620,39 +10605,19 @@
         <v>0</v>
       </c>
       <c r="Q344" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R344" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S344" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="345" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>401</v>
-      </c>
-      <c r="B345" s="4">
-        <v>45098</v>
-      </c>
-      <c r="O345" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P345" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q345" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="R345" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="S345" t="s">
-        <v>73</v>
-      </c>
+      <c r="O345" s="1"/>
+      <c r="Q345" s="1"/>
+      <c r="R345" s="1"/>
     </row>
     <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="O346" s="1"/>
@@ -10874,14 +10839,9 @@
       <c r="Q389" s="1"/>
       <c r="R389" s="1"/>
     </row>
-    <row r="390" spans="15:18" x14ac:dyDescent="0.25">
-      <c r="O390" s="1"/>
-      <c r="Q390" s="1"/>
-      <c r="R390" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S66">
-    <sortCondition ref="A2:A66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S65">
+    <sortCondition ref="A2:A65"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
